--- a/Base_Dados_Dashboard_GSP_2.0.xlsx
+++ b/Base_Dados_Dashboard_GSP_2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1012135\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D04BCAB-9C24-4F26-903B-490D57A57E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4CC58C-694B-4FE6-8087-2A30D8B69395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEIA-ME" sheetId="1" r:id="rId1"/>
@@ -191,12 +191,6 @@
   </si>
   <si>
     <t>varejo</t>
-  </si>
-  <si>
-    <t>pecas_distribuidores</t>
-  </si>
-  <si>
-    <t>pecas_varejo</t>
   </si>
   <si>
     <t>Preencher peças por canal conforme base definitiva do dashboard</t>
@@ -419,6 +413,12 @@
   </si>
   <si>
     <t>Local da imagem dentro do repositório</t>
+  </si>
+  <si>
+    <t>visitas_maio</t>
+  </si>
+  <si>
+    <t>visitas_junho</t>
   </si>
 </sst>
 </file>
@@ -6494,10 +6494,10 @@
         <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>24</v>
@@ -6519,10 +6519,14 @@
       <c r="E4" s="4">
         <v>114</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="F4" s="4">
+        <v>89</v>
+      </c>
+      <c r="G4" s="4">
+        <v>63</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
@@ -9261,7 +9265,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -9278,16 +9282,16 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>24</v>
@@ -9304,10 +9308,10 @@
         <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F4" s="4">
         <v>24</v>
@@ -12054,7 +12058,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -12073,22 +12077,22 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>24</v>
@@ -12102,10 +12106,10 @@
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="4">
         <v>6</v>
@@ -12117,7 +12121,7 @@
         <v/>
       </c>
       <c r="I4" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -12145,10 +12149,10 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" s="4">
         <v>8</v>
@@ -12160,7 +12164,7 @@
         <v/>
       </c>
       <c r="I5" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -12188,10 +12192,10 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4">
         <v>21</v>
@@ -12203,7 +12207,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -12231,10 +12235,10 @@
         <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" s="4">
         <v>9</v>
@@ -12246,7 +12250,7 @@
         <v/>
       </c>
       <c r="I7" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -12274,10 +12278,10 @@
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -12287,7 +12291,7 @@
         <v/>
       </c>
       <c r="I8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -12316,7 +12320,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -12353,7 +12357,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -14926,7 +14930,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -14945,22 +14949,22 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>24</v>
@@ -14974,13 +14978,13 @@
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -14989,7 +14993,7 @@
         <v/>
       </c>
       <c r="I4" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
@@ -15017,13 +15021,13 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -15058,13 +15062,13 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -15099,10 +15103,10 @@
         <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -17886,7 +17890,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -17903,19 +17907,19 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -17926,11 +17930,11 @@
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>28</v>
@@ -17964,11 +17968,11 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>32</v>
@@ -18002,11 +18006,11 @@
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>32</v>
@@ -18040,11 +18044,11 @@
         <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>32</v>
@@ -18080,7 +18084,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -20702,7 +20706,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -20711,19 +20715,19 @@
     </row>
     <row r="3" spans="1:26" ht="22.65" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -20731,16 +20735,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -20769,16 +20773,16 @@
         <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -20807,16 +20811,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -20845,16 +20849,16 @@
         <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -20883,16 +20887,16 @@
         <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -20921,16 +20925,16 @@
         <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -20959,16 +20963,16 @@
         <v>41</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
@@ -20994,19 +20998,19 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -21032,19 +21036,19 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>

--- a/Base_Dados_Dashboard_GSP_2.0.xlsx
+++ b/Base_Dados_Dashboard_GSP_2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1012135\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4CC58C-694B-4FE6-8087-2A30D8B69395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895CF9A0-03E0-4507-8AE2-B6E8E7600D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6520,7 +6520,7 @@
         <v>114</v>
       </c>
       <c r="F4" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" s="4">
         <v>63</v>
